--- a/public/exports/68534917.xlsx
+++ b/public/exports/68534917.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -364,7 +364,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016078</t>
+          <t xml:space="preserve">200016088</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">

--- a/public/exports/68534917.xlsx
+++ b/public/exports/68534917.xlsx
@@ -364,7 +364,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016088</t>
+          <t xml:space="preserve">200016078</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">

--- a/public/exports/68534917.xlsx
+++ b/public/exports/68534917.xlsx
@@ -416,40 +416,40 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solrød Center 3</t>
+          <t xml:space="preserve">Skolevej 51</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203386</t>
+          <t xml:space="preserve">8941987</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J6">
-        <v>1115</v>
+        <v>1586</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047379</t>
+          <t xml:space="preserve">200055903</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grontmij A/S</t>
+          <t xml:space="preserve">TopDahl ApS</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-29</t>
+          <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -491,40 +491,40 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 51</t>
+          <t xml:space="preserve">Tingsryds Alle 1B</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941987</t>
+          <t xml:space="preserve">2203980</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J7">
-        <v>1586</v>
+        <v>1771</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055903</t>
+          <t xml:space="preserve">311156883</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TopDahl ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-15</t>
+          <t xml:space="preserve">2026-02-03</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingsryds Alle 1B</t>
+          <t xml:space="preserve">Mosevej 13B</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -576,40 +576,40 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203980</t>
+          <t xml:space="preserve">2204990</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J8">
-        <v>1771</v>
+        <v>280</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">311156883</t>
+          <t xml:space="preserve">311211741</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-03</t>
+          <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosevej 13B</t>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -651,20 +651,20 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204990</t>
+          <t xml:space="preserve">2204674</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J9">
-        <v>280</v>
+        <v>355</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">311211741</t>
+          <t xml:space="preserve">311214136</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -716,30 +716,30 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnholmvej 10</t>
+          <t xml:space="preserve">Bistrupvang 36</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204674</t>
+          <t xml:space="preserve">2188168</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J10">
-        <v>355</v>
+        <v>792</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214136</t>
+          <t xml:space="preserve">311217330</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -791,30 +791,30 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrupvang 36</t>
+          <t xml:space="preserve">Poppelhegnet 32B</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188168</t>
+          <t xml:space="preserve">2203865</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J11">
-        <v>792</v>
+        <v>501</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217330</t>
+          <t xml:space="preserve">311217456</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppelhegnet 32B</t>
+          <t xml:space="preserve">Solrød Center 85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -876,20 +876,20 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203865</t>
+          <t xml:space="preserve">2203431</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J12">
-        <v>501</v>
+        <v>2288</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217456</t>
+          <t xml:space="preserve">311217395</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solrød Center 85</t>
+          <t xml:space="preserve">Tingsryds Alle 3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203431</t>
+          <t xml:space="preserve">2203441</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -960,11 +960,11 @@
         </is>
       </c>
       <c r="J13">
-        <v>2288</v>
+        <v>839</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217395</t>
+          <t xml:space="preserve">311217448</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1016,17 +1016,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingsryds Alle 3</t>
+          <t xml:space="preserve">Bistrupvang 35</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203441</t>
+          <t xml:space="preserve">2188167</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1035,11 +1035,11 @@
         </is>
       </c>
       <c r="J14">
-        <v>839</v>
+        <v>383</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217448</t>
+          <t xml:space="preserve">311217631</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-13</t>
+          <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrupvang 35</t>
+          <t xml:space="preserve">Solrød Center 1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188167</t>
+          <t xml:space="preserve">2203336</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1110,11 +1110,11 @@
         </is>
       </c>
       <c r="J15">
-        <v>383</v>
+        <v>3581</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217631</t>
+          <t xml:space="preserve">311217669</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solrød Center 1</t>
+          <t xml:space="preserve">Trylleskov Allé 3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203336</t>
+          <t xml:space="preserve">100036252</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1185,11 +1185,11 @@
         </is>
       </c>
       <c r="J16">
-        <v>3581</v>
+        <v>1252</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217669</t>
+          <t xml:space="preserve">311217682</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trylleskov Allé 3</t>
+          <t xml:space="preserve">Lindevej 15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">100036252</t>
+          <t xml:space="preserve">2187966</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1260,11 +1260,11 @@
         </is>
       </c>
       <c r="J17">
-        <v>1252</v>
+        <v>260</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217682</t>
+          <t xml:space="preserve">311217802</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-14</t>
+          <t xml:space="preserve">2026-12-15</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 15</t>
+          <t xml:space="preserve">Tjørnholmvej 12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2187966</t>
+          <t xml:space="preserve">2204117</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1335,11 +1335,11 @@
         </is>
       </c>
       <c r="J18">
-        <v>260</v>
+        <v>875</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217802</t>
+          <t xml:space="preserve">311217827</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnholmvej 12</t>
+          <t xml:space="preserve">Skolevej 51</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204117</t>
+          <t xml:space="preserve">8941987</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1410,11 +1410,11 @@
         </is>
       </c>
       <c r="J19">
-        <v>875</v>
+        <v>1690</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217827</t>
+          <t xml:space="preserve">311224721</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-15</t>
+          <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1481,15 +1481,15 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J20">
-        <v>1690</v>
+        <v>295</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224721</t>
+          <t xml:space="preserve">311224732</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1556,15 +1556,15 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J21">
-        <v>295</v>
+        <v>1384</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224732</t>
+          <t xml:space="preserve">311224734</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1631,15 +1631,15 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J22">
-        <v>1384</v>
+        <v>975</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224734</t>
+          <t xml:space="preserve">311224736</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1706,15 +1706,15 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J23">
-        <v>975</v>
+        <v>1102</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224736</t>
+          <t xml:space="preserve">311224724</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J24">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224724</t>
+          <t xml:space="preserve">311224727</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1856,15 +1856,15 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J25">
-        <v>1102</v>
+        <v>772</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224727</t>
+          <t xml:space="preserve">311224729</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1916,30 +1916,30 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 51</t>
+          <t xml:space="preserve">Christians Torv 124</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941987</t>
+          <t xml:space="preserve">2190312</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J26">
-        <v>772</v>
+        <v>11134</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224729</t>
+          <t xml:space="preserve">311231085</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-26</t>
+          <t xml:space="preserve">2027-02-28</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christians Torv 124</t>
+          <t xml:space="preserve">Den Lille Gade 20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2001,20 +2001,20 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2190312</t>
+          <t xml:space="preserve">8942093</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J27">
-        <v>11134</v>
+        <v>718</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231085</t>
+          <t xml:space="preserve">311238100</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-28</t>
+          <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2066,30 +2066,30 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Den Lille Gade 20</t>
+          <t xml:space="preserve">Skolevej 51</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942093</t>
+          <t xml:space="preserve">8941987</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J28">
-        <v>718</v>
+        <v>308</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238100</t>
+          <t xml:space="preserve">311238368</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-31</t>
+          <t xml:space="preserve">2027-04-02</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 51</t>
+          <t xml:space="preserve">Skolevej 53</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2156,15 +2156,15 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J29">
-        <v>308</v>
+        <v>775</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238368</t>
+          <t xml:space="preserve">311238367</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2216,30 +2216,30 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 53</t>
+          <t xml:space="preserve">Tingsryds Alle 27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941987</t>
+          <t xml:space="preserve">8942071</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J30">
-        <v>775</v>
+        <v>11333</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238367</t>
+          <t xml:space="preserve">311238369</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingsryds Alle 27</t>
+          <t xml:space="preserve">Engmosevej 14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2306,15 +2306,15 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J31">
-        <v>11333</v>
+        <v>1724</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238369</t>
+          <t xml:space="preserve">311238574</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-02</t>
+          <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engmosevej 14</t>
+          <t xml:space="preserve">Parkvej 11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2376,20 +2376,20 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942071</t>
+          <t xml:space="preserve">2189961</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J32">
-        <v>1724</v>
+        <v>719</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238574</t>
+          <t xml:space="preserve">311238422</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 11</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2451,20 +2451,20 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2189961</t>
+          <t xml:space="preserve">2190233</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J33">
-        <v>719</v>
+        <v>609</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238422</t>
+          <t xml:space="preserve">311238569</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2526,20 +2526,20 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2190233</t>
+          <t xml:space="preserve">2204674</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J34">
-        <v>609</v>
+        <v>1637</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238569</t>
+          <t xml:space="preserve">311238556</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2591,30 +2591,30 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 62</t>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941976</t>
+          <t xml:space="preserve">2204674</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J35">
-        <v>2266</v>
+        <v>2297</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238551</t>
+          <t xml:space="preserve">311238556</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2666,30 +2666,30 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 62</t>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941976</t>
+          <t xml:space="preserve">2204674</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J36">
-        <v>1889</v>
+        <v>2065</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238551</t>
+          <t xml:space="preserve">311238556</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2756,15 +2756,15 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J37">
-        <v>1637</v>
+        <v>2177</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238556</t>
+          <t xml:space="preserve">311238554</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnholmvej 10</t>
+          <t xml:space="preserve">Åsvej 14B</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2826,20 +2826,20 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204674</t>
+          <t xml:space="preserve">8942017</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J38">
-        <v>2297</v>
+        <v>2149</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238556</t>
+          <t xml:space="preserve">311238600</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnholmvej 10</t>
+          <t xml:space="preserve">Højagervænget 21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2901,20 +2901,20 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204674</t>
+          <t xml:space="preserve">8942087</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J39">
-        <v>2065</v>
+        <v>1902</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238556</t>
+          <t xml:space="preserve">311238732</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-04-04</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnholmvej 10</t>
+          <t xml:space="preserve">Højagervænget 21</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2976,20 +2976,20 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204674</t>
+          <t xml:space="preserve">8942087</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J40">
-        <v>2177</v>
+        <v>2493</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238554</t>
+          <t xml:space="preserve">311238734</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-04-04</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åsvej 14B</t>
+          <t xml:space="preserve">Langager 8</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942017</t>
+          <t xml:space="preserve">2202814</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3060,11 +3060,11 @@
         </is>
       </c>
       <c r="J41">
-        <v>2149</v>
+        <v>381</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238600</t>
+          <t xml:space="preserve">311238728</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-04-04</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højagervænget 21</t>
+          <t xml:space="preserve">Niels Juels Alle 2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942087</t>
+          <t xml:space="preserve">2189963</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3135,11 +3135,11 @@
         </is>
       </c>
       <c r="J42">
-        <v>1902</v>
+        <v>350</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238732</t>
+          <t xml:space="preserve">311238698</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højagervænget 21</t>
+          <t xml:space="preserve">Solrød Center 4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3201,20 +3201,20 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942087</t>
+          <t xml:space="preserve">267144, 267145</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J43">
-        <v>2493</v>
+        <v>4890</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238734</t>
+          <t xml:space="preserve">311238723</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langager 8</t>
+          <t xml:space="preserve">Vestre Grænsevej 34</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2202814</t>
+          <t xml:space="preserve">100003759</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3285,11 +3285,11 @@
         </is>
       </c>
       <c r="J44">
-        <v>381</v>
+        <v>431</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238728</t>
+          <t xml:space="preserve">311238740</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Juels Alle 2</t>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2189963</t>
+          <t xml:space="preserve">2204674</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3360,11 +3360,11 @@
         </is>
       </c>
       <c r="J45">
-        <v>350</v>
+        <v>1789</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238698</t>
+          <t xml:space="preserve">311298684</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-04</t>
+          <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solrød Center 4</t>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3426,20 +3426,20 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">267144, 267145</t>
+          <t xml:space="preserve">2204674</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J46">
-        <v>4890</v>
+        <v>1339</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238723</t>
+          <t xml:space="preserve">311298684</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-04</t>
+          <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Grænsevej 34</t>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3501,20 +3501,20 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">100003759</t>
+          <t xml:space="preserve">2204674</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J47">
-        <v>431</v>
+        <v>1448</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238740</t>
+          <t xml:space="preserve">311298684</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-04</t>
+          <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnholmvej 10</t>
+          <t xml:space="preserve">Havdrup Allé 6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204674</t>
+          <t xml:space="preserve">7717401</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3585,21 +3585,21 @@
         </is>
       </c>
       <c r="J48">
-        <v>1789</v>
+        <v>1372</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298684</t>
+          <t xml:space="preserve">311453702</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-20</t>
+          <t xml:space="preserve">2030-08-11</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnholmvej 10</t>
+          <t xml:space="preserve">Vestre Odinsvej 17</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3651,30 +3651,30 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204674</t>
+          <t xml:space="preserve">2203235</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J49">
-        <v>1339</v>
+        <v>339</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298684</t>
+          <t xml:space="preserve">311519279</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-20</t>
+          <t xml:space="preserve">2031-05-10</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3716,40 +3716,40 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnholmvej 10</t>
+          <t xml:space="preserve">Salbjergvej 26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204674</t>
+          <t xml:space="preserve">2188346</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J50">
-        <v>1448</v>
+        <v>328</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298684</t>
+          <t xml:space="preserve">311549361</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-20</t>
+          <t xml:space="preserve">2031-09-20</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3791,40 +3791,40 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havdrup Allé 6</t>
+          <t xml:space="preserve">Østre Strandvej 26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">7717401</t>
+          <t xml:space="preserve">2206014</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J51">
-        <v>1372</v>
+        <v>291</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311453702</t>
+          <t xml:space="preserve">311668910</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Klysner Consult ApS</t>
+          <t xml:space="preserve">ISOLINK ApS</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-08-11</t>
+          <t xml:space="preserve">2033-03-24</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Odinsvej 17</t>
+          <t xml:space="preserve">Egeparken 33A</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3876,30 +3876,30 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203235</t>
+          <t xml:space="preserve">259943, 259944, 259945, 259946, 259947, 259949, 259956, 259982, 259950, 259951, 259952, 259953, 259954, 259955, 259957, 259958, 259960, 259961, 259962, 259963, 259964, 259965, 259966, 259967, 259968, 259969, 259971, 259972, 259973, 259974, 259975, 259976, 259977, 259978, 259979, 259980, 259989, 259990, 259991, 259993, 259994, 259995</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J52">
-        <v>339</v>
+        <v>3906</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519279</t>
+          <t xml:space="preserve">311903759</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+          <t xml:space="preserve">Bang &amp; Beenfeldt A/S</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-10</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Salbjergvej 26</t>
+          <t xml:space="preserve">Skolevej 62</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3951,30 +3951,30 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188346</t>
+          <t xml:space="preserve">8941976</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J53">
-        <v>328</v>
+        <v>2266</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549361</t>
+          <t xml:space="preserve">311929920</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-20</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4016,40 +4016,40 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Strandvej 26</t>
+          <t xml:space="preserve">Skolevej 62</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2206014</t>
+          <t xml:space="preserve">8941976</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J54">
-        <v>291</v>
+        <v>1889</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668910</t>
+          <t xml:space="preserve">311929920</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISOLINK ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-24</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egeparken 33A</t>
+          <t xml:space="preserve">Solrød Center 3</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4101,30 +4101,30 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">259943, 259944, 259945, 259946, 259947, 259949, 259956, 259982, 259950, 259951, 259952, 259953, 259954, 259955, 259957, 259958, 259960, 259961, 259962, 259963, 259964, 259965, 259966, 259967, 259968, 259969, 259971, 259972, 259973, 259974, 259975, 259976, 259977, 259978, 259979, 259980, 259989, 259990, 259991, 259993, 259994, 259995</t>
+          <t xml:space="preserve">2203386</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J55">
-        <v>3906</v>
+        <v>1115</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903759</t>
+          <t xml:space="preserve">311929914</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bang &amp; Beenfeldt A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
